--- a/samples/ar_master_sample.xlsx
+++ b/samples/ar_master_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Critical Customers</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Receivable Balance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Credit Hold Position</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Account stop/open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Payment Terms</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Account Owner</t>
         </is>
@@ -474,21 +479,26 @@
           <t>Enterprise</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4500000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Aurelie Uguebou</t>
         </is>
@@ -510,21 +520,22 @@
           <t>Field Sales</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
         <v>670000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Olga Goudji</t>
         </is>
@@ -546,25 +557,30 @@
           <t>Telesales</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>500000</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>ALBERT DJONGA</t>
         </is>
@@ -586,21 +602,22 @@
           <t>New Customer</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
         <v>2400000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Aurelie Uguebou</t>
         </is>
@@ -622,21 +639,22 @@
           <t>Telesales</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
         <v>75000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Olga Goudji</t>
         </is>
@@ -646,13 +664,14 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
         <v>8145000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
